--- a/data_input/monthly/2025-09.xlsx
+++ b/data_input/monthly/2025-09.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00F3F2EE"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +56,11 @@
         <fgColor rgb="FFF2EFE6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F1F26"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -77,6 +86,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -646,36 +656,29 @@
   </sheetPr>
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>used</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>rev</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>disc</t>
         </is>

--- a/data_input/monthly/2025-09.xlsx
+++ b/data_input/monthly/2025-09.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="voucher_month" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="voucher_month" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
